--- a/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
+++ b/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
@@ -18,6 +18,7 @@
     <sheet name="7. Illustrative Example" sheetId="8" state="visible" r:id="rId10"/>
     <sheet name="8. Evaluation Metrics" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="9. Edge Cases" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="10. Exceptional DC Routing" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="310">
   <si>
     <t xml:space="preserve">Beat Planning &amp; Routing Agent — Cluster-Based Model</t>
   </si>
@@ -247,10 +248,10 @@
     <t xml:space="preserve">Rule</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Hard filter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exclude any cluster whose own intra-cluster distance alone would exceed the remaining travel budget — it cannot be completed even in isolation.</t>
+    <t xml:space="preserve">1. Ceiling check (conditional)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Check whether the DC's own required travel distance/time exceeds 80km / 180 minutes. If it does not, proceed with standard efficiency-ranked selection (Steps 2-4 below). If it does, the DC is reclassified as Exceptional — do NOT exclude it; instead route it using the BO Rule (strict BO-tier priority sequencing, see sheet "10. Exceptional DC Routing") in place of Steps 2-4.</t>
   </si>
   <si>
     <t xml:space="preserve">2. Rank by efficiency</t>
@@ -277,7 +278,7 @@
     <t xml:space="preserve">If budget remains after the greedy pass but no full cluster fits, fall back to individual BO-level selection within reach (see Edge Case: "All clusters exceed remaining budget").</t>
   </si>
   <si>
-    <t xml:space="preserve">Note: this greedy, rank-by-efficiency approach is the transparent/explainable approximation used in this workbook. The production Plan Generation Agent instead solves this as a Prize-Collecting VRP/Orienteering Problem via OR-Tools, which can find combinations the greedy pass would miss (e.g., two lower-ranked clusters that together beat one high-ranked cluster on a tight budget).</t>
+    <t xml:space="preserve">Note: this greedy, rank-by-efficiency approach is the transparent/explainable approximation used in this workbook. The production Plan Generation Agent instead solves this as a Prize-Collecting VRP/Orienteering Problem via OR-Tools, which can find combinations the greedy pass would miss (e.g., two lower-ranked clusters that together beat one high-ranked cluster on a tight budget). The conditional ceiling check (Step 1) applies before this greedy pass runs, so Exceptional DCs never reach the efficiency-ranking stage at all.</t>
   </si>
   <si>
     <t xml:space="preserve">Objective Function: Minimize Distance vs. Maximize Output</t>
@@ -310,7 +311,13 @@
     <t xml:space="preserve">This distinction matters operationally: a purely distance-minimizing route will look efficient on a map but may under-deliver on business outcomes; a purely output-maximizing route without a distance constraint is operationally infeasible for a single SE's working day. The model's job is to sit at the efficient frontier between the two — the highest CBS achievable within the hard travel ceiling.</t>
   </si>
   <si>
-    <t xml:space="preserve">Constraints Summary</t>
+    <t xml:space="preserve">Constraints Summary — Conditional Ceiling Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 80km / 180-minute ceiling is applied as a STANDARD constraint, not an absolute one. If a DC's (Distribution Center's) own BO density/spread inherently requires more than 80km or 180 minutes to cover — i.e., the DC itself cannot be served within the standard ceiling — it is reclassified as an Exceptional DC. Exceptional DCs are never dropped or skipped: a route is still generated for them, but routing switches from efficiency-ranked selection to the BO Rule (strict BO-tier priority sequencing). See sheet "10. Exceptional DC Routing" for the full logic.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Case</t>
   </si>
   <si>
     <t xml:space="preserve">Constraint</t>
@@ -334,7 +341,7 @@
     <t xml:space="preserve">Daily travel time</t>
   </si>
   <si>
-    <t xml:space="preserve">≤ 180 minutes (hard ceiling)</t>
+    <t xml:space="preserve">≤ 180 minutes</t>
   </si>
   <si>
     <t xml:space="preserve">Leaves working hours for actual BO visits, not just travel</t>
@@ -353,6 +360,60 @@
   </si>
   <si>
     <t xml:space="preserve">Prevents permanent starvation of low-density/low-tier clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route selection method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficiency-ranked (Score-per-km) greedy selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximizes output within the standard budget — see Section 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceptional Case (Conditional Trigger)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC's own required travel distance &gt; 80km, OR required travel time &gt; 180 minutes, to cover its assigned BOs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifies DCs that are structurally too sparse/spread out to fit the standard ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC flagged as "Exceptional DC" for that planning cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Separates it from standard optimization so it isn't silently truncated or dropped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceiling treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard 80km/180min ceiling is not used as a hard cutoff for this DC — it becomes a soft reference point, not a stop condition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ensures full BO coverage is still attempted rather than abandoning lower-priority BOs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Rule: strict priority sequencing by BO tier (BO1 -&gt; BO2 -&gt; BO3 -&gt; BO4 -&gt; BO5), not Score-per-km efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guarantees the highest-value BOs are always reached first, even at higher travel cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route generation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A route is still mandatorily generated for the Exceptional DC — it is never excluded from planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoids leaving any DC permanently unserved</t>
   </si>
   <si>
     <t xml:space="preserve">Technical Stack Reference</t>
@@ -690,6 +751,240 @@
   </si>
   <si>
     <t xml:space="preserve">Smooth recency_weight with a bounded decay curve (not a hard on/off) so score rises gradually rather than triggering sudden reprioritization spikes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC / cluster density exceeds the standard ceiling</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A DC's own BO spread inherently requires more than 80km or 180 minutes to cover, before any cross-DC optimization is even applied.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reclassify as an Exceptional DC (see "10. Exceptional DC Routing"). Do not exclude or truncate it — generate a route using the BO Rule (strict tier-priority sequencing: BO1 first, then BO2, etc.) instead of the standard Score-per-km efficiency ranking, so highest-value BOs are always reached even at higher travel cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceptional DC Routing — Conditional Ceiling &amp; the BO Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When a DC Becomes "Exceptional"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 80km / 180-minute ceiling is a STANDARD constraint, applied by default. But some DCs (Distribution Centers) are inherently sparse or geographically spread out — their own assigned BOs cannot be covered within 80km or 180 minutes even before any cross-DC route optimization is applied. Rather than truncating the route and silently dropping lower-ranked BOs (as the standard efficiency-ranked model would), such a DC is reclassified as Exceptional, and a dedicated route is still generated for it — sequenced by the BO Rule instead of Score-per-km.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The BO Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">For an Exceptional DC, cluster/BO selection switches from "maximize score-per-km" to strict BO-tier priority sequencing: visit all BO1 outlets first, then BO2, then BO3, and so on — regardless of the extra distance this requires. The standard ceiling becomes a soft reference point (used for monitoring/reporting) rather than a stop condition. Ties within the same tier are broken by recency urgency, then by nearest distance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sort all BOs in the Exceptional DC by tier ascending (BO1 = highest priority -&gt; BO5 = lowest).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within the same tier, break ties by recency urgency (longer since last visit goes first), then by nearest distance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sequence the route in this tier-priority order — do not stop at 80km/180min; continue until all BOs are covered or a defined maximum operational cap is reached.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flag any leg beyond the standard 80km/180km ceiling for visibility (e.g., in reporting/monitoring), even though it is not used to cut off the route.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DC "North Sparse Belt" has 6 BOs spread across a wide, low-density area. Edit the yellow input cells (BO tier, leg distance) and the priority rank, cumulative distance, and ceiling-exceeded flag recalculate automatically.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Code</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Distance (km)
+(from previous stop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Rank
+(BO Rule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cumulative Distance
+in BO-Rule Order (km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exceeds Standard
+Ceiling (80km)?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visited under
+BO Rule?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier Number
+(helper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priority Key
+(helper)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Score
+(tier-based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank
+(Efficiency order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Distance
+(Efficiency order, km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captured within
+80km? (Efficiency)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rank
+(Distance-ascending order)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cum. Distance
+(Distance order, km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Captured within
+80km? (Distance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier-&gt;Score
+lookup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL (full BO-Rule route)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard ceiling: 80km (reference only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under a STANDARD (efficiency-ranked) model truncated at 80km, this DC would drop whichever BOs fall past the cutoff — and which BOs get dropped depends entirely on the ordering used. The comparison below shows exactly that risk: only the BO Rule guarantees both BO1 outlets (the highest tier) are captured before any lower-tier BO, regardless of distance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This sheet's Priority Rank and Cumulative Distance columns use the same SUMIF-based ranking pattern as the standard Illustrative Example sheet — the only change is what the ranking key is (BO tier instead of Score-per-km) and that the ceiling is not used to cut the list short.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ceiling-Robustness Comparison: What Gets Left Out at 80km?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All three orderings below eventually cover the same 6 BOs (95km total) — that does not change with sequence. What changes is which BOs are already covered if the day is unexpectedly cut short at the 80km reference point. This is the real trade-off for an Exceptional DC: not total distance or total score, but which BOs are protected if the SE runs out of time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ordering</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ranking Basis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Order of Visits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOs Captured by 80km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score Captured by 80km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOs Left Out if Cut Short at 80km</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Rule (mandated)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO Tier ascending (BO1 -&gt; BO5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO101, BO102, BO201, BO202, BO301, BO401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO301, BO401 (both lower-tier — BO1/BO2 fully protected)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficiency (Score/km)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Score ÷ Distance, descending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO101, BO301, BO401, BO201, BO102, BO202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO202 only — but ordering is not guaranteed to protect top tiers first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Distance-Ascending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leg Distance, ascending (nearest first)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO401, BO301, BO101, BO201, BO202, BO102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BO102 — a BO1 (highest-tier) outlet left uncovered if cut short</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the core justification for the BO Rule: Score/km and Distance-ascending orderings can both, by coincidence of the data, end up capturing similar total score within 80km — but neither one guarantees WHICH BOs are protected. In this example, Distance-Ascending actually leaves out BO102, a top-tier (BO1) outlet, if the day is cut short — precisely the failure mode the BO Rule is designed to prevent. Only tier-first sequencing guarantees no higher-tier BO is ever left behind a lower-tier one, independent of how the day actually plays out.</t>
   </si>
 </sst>
 </file>
@@ -828,12 +1123,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
-        <bgColor rgb="FFFCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFE2EFDA"/>
         <bgColor rgb="FFDDEBF7"/>
       </patternFill>
@@ -842,6 +1131,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFCE4D6"/>
         <bgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF99"/>
+        <bgColor rgb="FFFCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -900,7 +1195,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -949,15 +1244,35 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -966,14 +1281,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1009,7 +1316,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1017,27 +1324,19 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="165" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1051,6 +1350,14 @@
     </xf>
     <xf numFmtId="165" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1473,7 +1780,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -1483,7 +1790,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1493,139 +1800,996 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>184</v>
+        <v>204</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>216</v>
+        <v>236</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>238</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:T36"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="1" width="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="5" t="s">
+        <v>244</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="H16" s="6" t="s">
+        <v>262</v>
+      </c>
+      <c r="I16" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="J16" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="K16" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="N16" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="O16" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="P16" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q16" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="R16" s="39" t="s">
+        <v>271</v>
+      </c>
+      <c r="S16" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="T16" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="18" t="n">
+        <f aca="false">RANK(I17,$I$17:$I$22,1)</f>
+        <v>1</v>
+      </c>
+      <c r="E17" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D17,$C$17:$C$22)</f>
+        <v>12</v>
+      </c>
+      <c r="F17" s="18" t="str">
+        <f aca="false">IF(E17&gt;80,"Yes — over ceiling","No")</f>
+        <v>No</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H17" s="15" t="n">
+        <f aca="false">VALUE(MID(B17,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I17" s="20" t="n">
+        <f aca="false">H17+C17/10000</f>
+        <v>1.0012</v>
+      </c>
+      <c r="J17" s="15" t="n">
+        <f aca="false">VLOOKUP(B17,$S$17:$T$21,2,FALSE())</f>
+        <v>100</v>
+      </c>
+      <c r="K17" s="17" t="n">
+        <f aca="false">IFERROR(J17/C17,0)</f>
+        <v>8.33333333333333</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <f aca="false">RANK(K17,$K$17:$K$22,0)+COUNTIF($K$17:K17,K17)-1</f>
+        <v>1</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L17,$C$17:$C$22)</f>
+        <v>12</v>
+      </c>
+      <c r="N17" s="21" t="str">
+        <f aca="false">IF(M17&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="O17" s="22" t="n">
+        <f aca="false">RANK(C17,$C$17:$C$22,1)+COUNTIF($C$17:C17,C17)-1</f>
+        <v>3</v>
+      </c>
+      <c r="P17" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O17,$C$17:$C$22)</f>
+        <v>30</v>
+      </c>
+      <c r="Q17" s="23" t="str">
+        <f aca="false">IF(P17&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="S17" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="T17" s="24" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>275</v>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="18" t="n">
+        <f aca="false">RANK(I18,$I$17:$I$22,1)</f>
+        <v>2</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D18,$C$17:$C$22)</f>
+        <v>37</v>
+      </c>
+      <c r="F18" s="18" t="str">
+        <f aca="false">IF(E18&gt;80,"Yes — over ceiling","No")</f>
+        <v>No</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H18" s="15" t="n">
+        <f aca="false">VALUE(MID(B18,3,1))</f>
+        <v>1</v>
+      </c>
+      <c r="I18" s="20" t="n">
+        <f aca="false">H18+C18/10000</f>
+        <v>1.0025</v>
+      </c>
+      <c r="J18" s="15" t="n">
+        <f aca="false">VLOOKUP(B18,$S$17:$T$21,2,FALSE())</f>
+        <v>100</v>
+      </c>
+      <c r="K18" s="17" t="n">
+        <f aca="false">IFERROR(J18/C18,0)</f>
+        <v>4</v>
+      </c>
+      <c r="L18" s="20" t="n">
+        <f aca="false">RANK(K18,$K$17:$K$22,0)+COUNTIF($K$17:K18,K18)-1</f>
+        <v>5</v>
+      </c>
+      <c r="M18" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L18,$C$17:$C$22)</f>
+        <v>73</v>
+      </c>
+      <c r="N18" s="21" t="str">
+        <f aca="false">IF(M18&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="O18" s="22" t="n">
+        <f aca="false">RANK(C18,$C$17:$C$22,1)+COUNTIF($C$17:C18,C18)-1</f>
+        <v>6</v>
+      </c>
+      <c r="P18" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O18,$C$17:$C$22)</f>
+        <v>95</v>
+      </c>
+      <c r="Q18" s="23" t="str">
+        <f aca="false">IF(P18&lt;=80,"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="S18" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="T18" s="24" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C19" s="16" t="n">
+        <v>18</v>
+      </c>
+      <c r="D19" s="18" t="n">
+        <f aca="false">RANK(I19,$I$17:$I$22,1)</f>
+        <v>3</v>
+      </c>
+      <c r="E19" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D19,$C$17:$C$22)</f>
+        <v>55</v>
+      </c>
+      <c r="F19" s="18" t="str">
+        <f aca="false">IF(E19&gt;80,"Yes — over ceiling","No")</f>
+        <v>No</v>
+      </c>
+      <c r="G19" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H19" s="15" t="n">
+        <f aca="false">VALUE(MID(B19,3,1))</f>
+        <v>2</v>
+      </c>
+      <c r="I19" s="20" t="n">
+        <f aca="false">H19+C19/10000</f>
+        <v>2.0018</v>
+      </c>
+      <c r="J19" s="15" t="n">
+        <f aca="false">VLOOKUP(B19,$S$17:$T$21,2,FALSE())</f>
+        <v>80</v>
+      </c>
+      <c r="K19" s="17" t="n">
+        <f aca="false">IFERROR(J19/C19,0)</f>
+        <v>4.44444444444445</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <f aca="false">RANK(K19,$K$17:$K$22,0)+COUNTIF($K$17:K19,K19)-1</f>
+        <v>4</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L19,$C$17:$C$22)</f>
+        <v>48</v>
+      </c>
+      <c r="N19" s="21" t="str">
+        <f aca="false">IF(M19&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="O19" s="22" t="n">
+        <f aca="false">RANK(C19,$C$17:$C$22,1)+COUNTIF($C$17:C19,C19)-1</f>
+        <v>4</v>
+      </c>
+      <c r="P19" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O19,$C$17:$C$22)</f>
+        <v>48</v>
+      </c>
+      <c r="Q19" s="23" t="str">
+        <f aca="false">IF(P19&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="S19" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="T19" s="24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>277</v>
+      </c>
+      <c r="C20" s="16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" s="18" t="n">
+        <f aca="false">RANK(I20,$I$17:$I$22,1)</f>
+        <v>4</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D20,$C$17:$C$22)</f>
+        <v>77</v>
+      </c>
+      <c r="F20" s="18" t="str">
+        <f aca="false">IF(E20&gt;80,"Yes — over ceiling","No")</f>
+        <v>No</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H20" s="15" t="n">
+        <f aca="false">VALUE(MID(B20,3,1))</f>
+        <v>2</v>
+      </c>
+      <c r="I20" s="20" t="n">
+        <f aca="false">H20+C20/10000</f>
+        <v>2.0022</v>
+      </c>
+      <c r="J20" s="15" t="n">
+        <f aca="false">VLOOKUP(B20,$S$17:$T$21,2,FALSE())</f>
+        <v>80</v>
+      </c>
+      <c r="K20" s="17" t="n">
+        <f aca="false">IFERROR(J20/C20,0)</f>
+        <v>3.63636363636364</v>
+      </c>
+      <c r="L20" s="20" t="n">
+        <f aca="false">RANK(K20,$K$17:$K$22,0)+COUNTIF($K$17:K20,K20)-1</f>
+        <v>6</v>
+      </c>
+      <c r="M20" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L20,$C$17:$C$22)</f>
+        <v>95</v>
+      </c>
+      <c r="N20" s="21" t="str">
+        <f aca="false">IF(M20&lt;=80,"Y","N")</f>
+        <v>N</v>
+      </c>
+      <c r="O20" s="22" t="n">
+        <f aca="false">RANK(C20,$C$17:$C$22,1)+COUNTIF($C$17:C20,C20)-1</f>
+        <v>5</v>
+      </c>
+      <c r="P20" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O20,$C$17:$C$22)</f>
+        <v>70</v>
+      </c>
+      <c r="Q20" s="23" t="str">
+        <f aca="false">IF(P20&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="S20" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="T20" s="24" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>279</v>
+      </c>
+      <c r="C21" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D21" s="18" t="n">
+        <f aca="false">RANK(I21,$I$17:$I$22,1)</f>
+        <v>5</v>
+      </c>
+      <c r="E21" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D21,$C$17:$C$22)</f>
+        <v>87</v>
+      </c>
+      <c r="F21" s="18" t="str">
+        <f aca="false">IF(E21&gt;80,"Yes — over ceiling","No")</f>
+        <v>Yes — over ceiling</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H21" s="15" t="n">
+        <f aca="false">VALUE(MID(B21,3,1))</f>
+        <v>3</v>
+      </c>
+      <c r="I21" s="20" t="n">
+        <f aca="false">H21+C21/10000</f>
+        <v>3.001</v>
+      </c>
+      <c r="J21" s="15" t="n">
+        <f aca="false">VLOOKUP(B21,$S$17:$T$21,2,FALSE())</f>
+        <v>60</v>
+      </c>
+      <c r="K21" s="17" t="n">
+        <f aca="false">IFERROR(J21/C21,0)</f>
+        <v>6</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <f aca="false">RANK(K21,$K$17:$K$22,0)+COUNTIF($K$17:K21,K21)-1</f>
+        <v>2</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L21,$C$17:$C$22)</f>
+        <v>22</v>
+      </c>
+      <c r="N21" s="21" t="str">
+        <f aca="false">IF(M21&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="O21" s="22" t="n">
+        <f aca="false">RANK(C21,$C$17:$C$22,1)+COUNTIF($C$17:C21,C21)-1</f>
+        <v>2</v>
+      </c>
+      <c r="P21" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O21,$C$17:$C$22)</f>
+        <v>18</v>
+      </c>
+      <c r="Q21" s="23" t="str">
+        <f aca="false">IF(P21&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="S21" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="T21" s="24" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>281</v>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="18" t="n">
+        <f aca="false">RANK(I22,$I$17:$I$22,1)</f>
+        <v>6</v>
+      </c>
+      <c r="E22" s="18" t="n">
+        <f aca="false">SUMIF($D$17:$D$22,"&lt;="&amp;D22,$C$17:$C$22)</f>
+        <v>95</v>
+      </c>
+      <c r="F22" s="18" t="str">
+        <f aca="false">IF(E22&gt;80,"Yes — over ceiling","No")</f>
+        <v>Yes — over ceiling</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="H22" s="15" t="n">
+        <f aca="false">VALUE(MID(B22,3,1))</f>
+        <v>4</v>
+      </c>
+      <c r="I22" s="20" t="n">
+        <f aca="false">H22+C22/10000</f>
+        <v>4.0008</v>
+      </c>
+      <c r="J22" s="15" t="n">
+        <f aca="false">VLOOKUP(B22,$S$17:$T$21,2,FALSE())</f>
+        <v>40</v>
+      </c>
+      <c r="K22" s="17" t="n">
+        <f aca="false">IFERROR(J22/C22,0)</f>
+        <v>5</v>
+      </c>
+      <c r="L22" s="20" t="n">
+        <f aca="false">RANK(K22,$K$17:$K$22,0)+COUNTIF($K$17:K22,K22)-1</f>
+        <v>3</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <f aca="false">SUMIF($L$17:$L$22,"&lt;="&amp;L22,$C$17:$C$22)</f>
+        <v>30</v>
+      </c>
+      <c r="N22" s="21" t="str">
+        <f aca="false">IF(M22&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+      <c r="O22" s="22" t="n">
+        <f aca="false">RANK(C22,$C$17:$C$22,1)+COUNTIF($C$17:C22,C22)-1</f>
+        <v>1</v>
+      </c>
+      <c r="P22" s="22" t="n">
+        <f aca="false">SUMIF($O$17:$O$22,"&lt;="&amp;O22,$C$17:$C$22)</f>
+        <v>8</v>
+      </c>
+      <c r="Q22" s="23" t="str">
+        <f aca="false">IF(P22&lt;=80,"Y","N")</f>
+        <v>Y</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="40" t="s">
+        <v>285</v>
+      </c>
+      <c r="B23" s="40"/>
+      <c r="C23" s="27" t="n">
+        <f aca="false">SUM(C17:C22)</f>
+        <v>95</v>
+      </c>
+      <c r="F23" s="29" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="5" t="s">
+        <v>287</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="5"/>
+    </row>
+    <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+    </row>
+    <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
+      <c r="P29" s="4"/>
+      <c r="Q29" s="4"/>
+    </row>
+    <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+      <c r="L30" s="5"/>
+      <c r="M30" s="5"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="5"/>
+      <c r="P30" s="5"/>
+      <c r="Q30" s="5"/>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>299</v>
+      </c>
+      <c r="D32" s="18" t="str">
+        <f aca="false">SUMPRODUCT(--(F17:F22="No"))&amp;" of 6"</f>
+        <v>4 of 6</v>
+      </c>
+      <c r="E32" s="18" t="n">
+        <f aca="false">SUMIF(F17:F22,"No",J17:J22)</f>
+        <v>360</v>
+      </c>
+      <c r="F32" s="13" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>303</v>
+      </c>
+      <c r="D33" s="20" t="str">
+        <f aca="false">SUMPRODUCT(--(N17:N22="Y"))&amp;" of 6"</f>
+        <v>5 of 6</v>
+      </c>
+      <c r="E33" s="20" t="n">
+        <f aca="false">SUMIF(N17:N22,"Y",J17:J22)</f>
+        <v>380</v>
+      </c>
+      <c r="F33" s="14" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="B34" s="37" t="s">
+        <v>306</v>
+      </c>
+      <c r="C34" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="D34" s="22" t="str">
+        <f aca="false">SUMPRODUCT(--(Q17:Q22="Y"))&amp;" of 6"</f>
+        <v>5 of 6</v>
+      </c>
+      <c r="E34" s="22" t="n">
+        <f aca="false">SUMIF(Q17:Q22,"Y",J17:J22)</f>
+        <v>360</v>
+      </c>
+      <c r="F34" s="37" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="5"/>
+      <c r="L36" s="5"/>
+      <c r="M36" s="5"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="5"/>
+      <c r="P36" s="5"/>
+      <c r="Q36" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="A29:Q29"/>
+    <mergeCell ref="A30:Q30"/>
+    <mergeCell ref="A36:Q36"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2035,7 +3199,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="s">
         <v>72</v>
       </c>
@@ -2225,12 +3389,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2243,64 +3406,174 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
     </row>
-    <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+    <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+    </row>
+    <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="C4" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="B6" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="C6" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="8" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="13" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="B7" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="C7" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="C6" s="7" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="13" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="8" t="s">
+      <c r="B8" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="C8" s="13" t="s">
         <v>107</v>
       </c>
     </row>
+    <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+    </row>
+    <row r="13" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="14" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" s="14" t="s">
+        <v>127</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A4:F4"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2326,7 +3599,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2336,7 +3609,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>26</v>
@@ -2344,42 +3617,42 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>116</v>
+        <v>136</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>117</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>
@@ -2408,17 +3681,17 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="15"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2430,7 +3703,7 @@
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -2442,500 +3715,500 @@
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>144</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>128</v>
+        <v>148</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>131</v>
+        <v>151</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>132</v>
+        <v>152</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>139</v>
-      </c>
-      <c r="B6" s="13" t="n">
+      <c r="A6" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="16" t="n">
         <v>8</v>
       </c>
-      <c r="C6" s="13" t="n">
+      <c r="C6" s="16" t="n">
         <v>92</v>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="15" t="n">
         <f aca="false">D6+E6</f>
         <v>10</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="17" t="n">
         <f aca="false">IFERROR(C6/F6,0)</f>
         <v>9.2</v>
       </c>
-      <c r="H6" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I6" s="15" t="n">
+      <c r="H6" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I6" s="18" t="n">
         <f aca="false">RANK(G6,$G$6:$G$11,0)+COUNTIF($G$6:G6,G6)-1</f>
         <v>2</v>
       </c>
-      <c r="J6" s="15" t="n">
+      <c r="J6" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I6,$F$6:$F$11)</f>
         <v>15</v>
       </c>
-      <c r="K6" s="16" t="str">
+      <c r="K6" s="19" t="str">
         <f aca="false">IF(J6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="20" t="n">
         <f aca="false">RANK(C6,$C$6:$C$11,0)+COUNTIF($C$6:C6,C6)-1</f>
         <v>1</v>
       </c>
-      <c r="M6" s="17" t="n">
+      <c r="M6" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L6,$F$6:$F$11)</f>
         <v>10</v>
       </c>
-      <c r="N6" s="18" t="str">
+      <c r="N6" s="21" t="str">
         <f aca="false">IF(M6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O6" s="19" t="n">
+      <c r="O6" s="22" t="n">
         <f aca="false">RANK(F6,$F$6:$F$11,1)+COUNTIF($F$6:F6,F6)-1</f>
         <v>3</v>
       </c>
-      <c r="P6" s="19" t="n">
+      <c r="P6" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O6,$F$6:$F$11)</f>
         <v>23</v>
       </c>
-      <c r="Q6" s="20" t="str">
+      <c r="Q6" s="23" t="str">
         <f aca="false">IF(P6&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B7" s="13" t="n">
+      <c r="A7" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="16" t="n">
         <v>61</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="16" t="n">
         <v>9</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="24" t="n">
         <f aca="false">D7+E7</f>
         <v>13</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <f aca="false">IFERROR(C7/F7,0)</f>
         <v>4.69230769230769</v>
       </c>
-      <c r="H7" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I7" s="15" t="n">
+      <c r="H7" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I7" s="18" t="n">
         <f aca="false">RANK(G7,$G$6:$G$11,0)+COUNTIF($G$6:G7,G7)-1</f>
         <v>3</v>
       </c>
-      <c r="J7" s="15" t="n">
+      <c r="J7" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I7,$F$6:$F$11)</f>
         <v>28</v>
       </c>
-      <c r="K7" s="16" t="str">
+      <c r="K7" s="19" t="str">
         <f aca="false">IF(J7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="20" t="n">
         <f aca="false">RANK(C7,$C$6:$C$11,0)+COUNTIF($C$6:C7,C7)-1</f>
         <v>4</v>
       </c>
-      <c r="M7" s="17" t="n">
+      <c r="M7" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L7,$F$6:$F$11)</f>
         <v>75</v>
       </c>
-      <c r="N7" s="18" t="str">
+      <c r="N7" s="21" t="str">
         <f aca="false">IF(M7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O7" s="19" t="n">
+      <c r="O7" s="22" t="n">
         <f aca="false">RANK(F7,$F$6:$F$11,1)+COUNTIF($F$6:F7,F7)-1</f>
         <v>4</v>
       </c>
-      <c r="P7" s="19" t="n">
+      <c r="P7" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O7,$F$6:$F$11)</f>
         <v>36</v>
       </c>
-      <c r="Q7" s="20" t="str">
+      <c r="Q7" s="23" t="str">
         <f aca="false">IF(P7&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="B8" s="13" t="n">
+      <c r="A8" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="16" t="n">
         <v>12</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="16" t="n">
         <v>78</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="16" t="n">
         <v>15</v>
       </c>
-      <c r="F8" s="12" t="n">
+      <c r="F8" s="15" t="n">
         <f aca="false">D8+E8</f>
         <v>25</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="17" t="n">
         <f aca="false">IFERROR(C8/F8,0)</f>
         <v>3.12</v>
       </c>
-      <c r="H8" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="I8" s="15" t="n">
+      <c r="H8" s="16" t="s">
+        <v>163</v>
+      </c>
+      <c r="I8" s="18" t="n">
         <f aca="false">RANK(G8,$G$6:$G$11,0)+COUNTIF($G$6:G8,G8)-1</f>
         <v>6</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I8,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="K8" s="16" t="str">
+      <c r="K8" s="19" t="str">
         <f aca="false">IF(J8&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="20" t="n">
         <f aca="false">RANK(C8,$C$6:$C$11,0)+COUNTIF($C$6:C8,C8)-1</f>
         <v>3</v>
       </c>
-      <c r="M8" s="17" t="n">
+      <c r="M8" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L8,$F$6:$F$11)</f>
         <v>62</v>
       </c>
-      <c r="N8" s="18" t="str">
+      <c r="N8" s="21" t="str">
         <f aca="false">IF(M8&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O8" s="19" t="n">
+      <c r="O8" s="22" t="n">
         <f aca="false">RANK(F8,$F$6:$F$11,1)+COUNTIF($F$6:F8,F8)-1</f>
         <v>5</v>
       </c>
-      <c r="P8" s="19" t="n">
+      <c r="P8" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O8,$F$6:$F$11)</f>
         <v>61</v>
       </c>
-      <c r="Q8" s="20" t="str">
+      <c r="Q8" s="23" t="str">
         <f aca="false">IF(P8&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B9" s="13" t="n">
+      <c r="A9" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="16" t="n">
         <v>55</v>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="24" t="n">
         <f aca="false">D9+E9</f>
         <v>5</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="25" t="n">
         <f aca="false">IFERROR(C9/F9,0)</f>
         <v>11</v>
       </c>
-      <c r="H9" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I9" s="15" t="n">
+      <c r="H9" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I9" s="18" t="n">
         <f aca="false">RANK(G9,$G$6:$G$11,0)+COUNTIF($G$6:G9,G9)-1</f>
         <v>1</v>
       </c>
-      <c r="J9" s="15" t="n">
+      <c r="J9" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I9,$F$6:$F$11)</f>
         <v>5</v>
       </c>
-      <c r="K9" s="16" t="str">
+      <c r="K9" s="19" t="str">
         <f aca="false">IF(J9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="20" t="n">
         <f aca="false">RANK(C9,$C$6:$C$11,0)+COUNTIF($C$6:C9,C9)-1</f>
         <v>5</v>
       </c>
-      <c r="M9" s="17" t="n">
+      <c r="M9" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L9,$F$6:$F$11)</f>
         <v>80</v>
       </c>
-      <c r="N9" s="18" t="str">
+      <c r="N9" s="21" t="str">
         <f aca="false">IF(M9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O9" s="19" t="n">
+      <c r="O9" s="22" t="n">
         <f aca="false">RANK(F9,$F$6:$F$11,1)+COUNTIF($F$6:F9,F9)-1</f>
         <v>1</v>
       </c>
-      <c r="P9" s="19" t="n">
+      <c r="P9" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O9,$F$6:$F$11)</f>
         <v>5</v>
       </c>
-      <c r="Q9" s="20" t="str">
+      <c r="Q9" s="23" t="str">
         <f aca="false">IF(P9&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>145</v>
-      </c>
-      <c r="B10" s="13" t="n">
+      <c r="A10" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="B10" s="16" t="n">
         <v>7</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="16" t="n">
         <v>88</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="16" t="n">
         <v>22</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="15" t="n">
         <f aca="false">D10+E10</f>
         <v>27</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="17" t="n">
         <f aca="false">IFERROR(C10/F10,0)</f>
         <v>3.25925925925926</v>
       </c>
-      <c r="H10" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I10" s="15" t="n">
+      <c r="H10" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I10" s="18" t="n">
         <f aca="false">RANK(G10,$G$6:$G$11,0)+COUNTIF($G$6:G10,G10)-1</f>
         <v>5</v>
       </c>
-      <c r="J10" s="15" t="n">
+      <c r="J10" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I10,$F$6:$F$11)</f>
         <v>63</v>
       </c>
-      <c r="K10" s="16" t="str">
+      <c r="K10" s="19" t="str">
         <f aca="false">IF(J10&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="20" t="n">
         <f aca="false">RANK(C10,$C$6:$C$11,0)+COUNTIF($C$6:C10,C10)-1</f>
         <v>2</v>
       </c>
-      <c r="M10" s="17" t="n">
+      <c r="M10" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L10,$F$6:$F$11)</f>
         <v>37</v>
       </c>
-      <c r="N10" s="18" t="str">
+      <c r="N10" s="21" t="str">
         <f aca="false">IF(M10&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="O10" s="19" t="n">
+      <c r="O10" s="22" t="n">
         <f aca="false">RANK(F10,$F$6:$F$11,1)+COUNTIF($F$6:F10,F10)-1</f>
         <v>6</v>
       </c>
-      <c r="P10" s="19" t="n">
+      <c r="P10" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O10,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="Q10" s="20" t="str">
+      <c r="Q10" s="23" t="str">
         <f aca="false">IF(P10&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B11" s="13" t="n">
+      <c r="A11" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="16" t="n">
         <v>30</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="24" t="n">
         <f aca="false">D11+E11</f>
         <v>8</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="25" t="n">
         <f aca="false">IFERROR(C11/F11,0)</f>
         <v>3.75</v>
       </c>
-      <c r="H11" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="I11" s="15" t="n">
+      <c r="H11" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="I11" s="18" t="n">
         <f aca="false">RANK(G11,$G$6:$G$11,0)+COUNTIF($G$6:G11,G11)-1</f>
         <v>4</v>
       </c>
-      <c r="J11" s="15" t="n">
+      <c r="J11" s="18" t="n">
         <f aca="false">SUMIF($I$6:$I$11,"&lt;="&amp;I11,$F$6:$F$11)</f>
         <v>36</v>
       </c>
-      <c r="K11" s="16" t="str">
+      <c r="K11" s="19" t="str">
         <f aca="false">IF(J11&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="20" t="n">
         <f aca="false">RANK(C11,$C$6:$C$11,0)+COUNTIF($C$6:C11,C11)-1</f>
         <v>6</v>
       </c>
-      <c r="M11" s="17" t="n">
+      <c r="M11" s="20" t="n">
         <f aca="false">SUMIF($L$6:$L$11,"&lt;="&amp;L11,$F$6:$F$11)</f>
         <v>88</v>
       </c>
-      <c r="N11" s="18" t="str">
+      <c r="N11" s="21" t="str">
         <f aca="false">IF(M11&lt;=80,"Y","N")</f>
         <v>N</v>
       </c>
-      <c r="O11" s="19" t="n">
+      <c r="O11" s="22" t="n">
         <f aca="false">RANK(F11,$F$6:$F$11,1)+COUNTIF($F$6:F11,F11)-1</f>
         <v>2</v>
       </c>
-      <c r="P11" s="19" t="n">
+      <c r="P11" s="22" t="n">
         <f aca="false">SUMIF($O$6:$O$11,"&lt;="&amp;O11,$F$6:$F$11)</f>
         <v>13</v>
       </c>
-      <c r="Q11" s="20" t="str">
+      <c r="Q11" s="23" t="str">
         <f aca="false">IF(P11&lt;=80,"Y","N")</f>
         <v>Y</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="24" t="n">
+      <c r="A12" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="27" t="n">
         <f aca="false">SUMIF(H6:H11,"Y",F6:F11)</f>
         <v>63</v>
       </c>
-      <c r="G12" s="25" t="n">
+      <c r="G12" s="28" t="n">
         <f aca="false">SUMIF(H6:H11,"Y",C6:C11)</f>
         <v>326</v>
       </c>
-      <c r="H12" s="26" t="s">
-        <v>148</v>
+      <c r="H12" s="29" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="24" t="n">
+      <c r="A13" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="27" t="n">
         <f aca="false">SUMIF(K6:K11,"Y",F6:F11)</f>
         <v>63</v>
       </c>
-      <c r="G13" s="25" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">SUMIF(K6:K11,"Y",C6:C11)</f>
         <v>326</v>
       </c>
-      <c r="H13" s="26" t="s">
-        <v>148</v>
-      </c>
-      <c r="M13" s="18" t="n">
+      <c r="H13" s="29" t="s">
+        <v>168</v>
+      </c>
+      <c r="M13" s="21" t="n">
         <f aca="false">SUMIF(N6:N11,"Y",F6:F11)</f>
         <v>80</v>
       </c>
-      <c r="N13" s="27" t="n">
+      <c r="N13" s="30" t="n">
         <f aca="false">SUMIF(N6:N11,"Y",C6:C11)</f>
         <v>374</v>
       </c>
-      <c r="P13" s="20" t="n">
+      <c r="P13" s="23" t="n">
         <f aca="false">SUMIF(Q6:Q11,"Y",F6:F11)</f>
         <v>61</v>
       </c>
-      <c r="Q13" s="28" t="n">
+      <c r="Q13" s="31" t="n">
         <f aca="false">SUMIF(Q6:Q11,"Y",C6:C11)</f>
         <v>316</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2947,7 +4220,7 @@
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>151</v>
+        <v>171</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -2959,7 +4232,7 @@
     </row>
     <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -2971,7 +4244,7 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2992,7 +4265,7 @@
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -3013,96 +4286,96 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="30" t="s">
-        <v>163</v>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="A21" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="B21" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C21" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="18" t="n">
         <f aca="false">F13</f>
         <v>63</v>
       </c>
-      <c r="E21" s="31" t="n">
+      <c r="E21" s="33" t="n">
         <f aca="false">G13</f>
         <v>326</v>
       </c>
-      <c r="F21" s="31" t="n">
+      <c r="F21" s="33" t="n">
         <f aca="false">IFERROR(G13/F13,0)</f>
         <v>5.17460317460318</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="C22" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="D22" s="17" t="n">
+      <c r="A22" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="C22" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="20" t="n">
         <f aca="false">M13</f>
         <v>80</v>
       </c>
-      <c r="E22" s="34" t="n">
+      <c r="E22" s="35" t="n">
         <f aca="false">N13</f>
         <v>374</v>
       </c>
-      <c r="F22" s="34" t="n">
+      <c r="F22" s="35" t="n">
         <f aca="false">IFERROR(N13/M13,0)</f>
         <v>4.675</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="B23" s="36" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="36" t="s">
-        <v>169</v>
-      </c>
-      <c r="D23" s="19" t="n">
+      <c r="A23" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="C23" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="D23" s="22" t="n">
         <f aca="false">P13</f>
         <v>61</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="38" t="n">
         <f aca="false">Q13</f>
         <v>316</v>
       </c>
-      <c r="F23" s="37" t="n">
+      <c r="F23" s="38" t="n">
         <f aca="false">IFERROR(Q13/P13,0)</f>
         <v>5.18032786885246</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -3158,7 +4431,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3168,7 +4441,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>50</v>
@@ -3176,34 +4449,34 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>

--- a/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
+++ b/Routing_agent/Beat_Planning_Routing_Agent_Cluster_Model.xlsx
@@ -19,6 +19,7 @@
     <sheet name="8. Evaluation Metrics" sheetId="9" state="visible" r:id="rId11"/>
     <sheet name="9. Edge Cases" sheetId="10" state="visible" r:id="rId12"/>
     <sheet name="10. Exceptional DC Routing" sheetId="11" state="visible" r:id="rId13"/>
+    <sheet name="11. Route Distinction Rule" sheetId="12" state="visible" r:id="rId14"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="389">
   <si>
     <t xml:space="preserve">Beat Planning &amp; Routing Agent — Cluster-Based Model</t>
   </si>
@@ -279,6 +280,9 @@
   </si>
   <si>
     <t xml:space="preserve">Note: this greedy, rank-by-efficiency approach is the transparent/explainable approximation used in this workbook. The production Plan Generation Agent instead solves this as a Prize-Collecting VRP/Orienteering Problem via OR-Tools, which can find combinations the greedy pass would miss (e.g., two lower-ranked clusters that together beat one high-ranked cluster on a tight budget). The conditional ceiling check (Step 1) applies before this greedy pass runs, so Exceptional DCs never reach the efficiency-ranking stage at all.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route Distinction / Beat Cycle: none of the steps above, on their own, guarantee that consecutive routes differ or that every cluster gets a predictable visit cadence — only recency decay (Section 2) provides a soft nudge in that direction. See sheet "11. Route Distinction Rule" for the explicit Repeat-Avoidance and Fixed Rotation models that address this gap.</t>
   </si>
   <si>
     <t xml:space="preserve">Objective Function: Minimize Distance vs. Maximize Output</t>
@@ -762,6 +766,15 @@
     <t xml:space="preserve">Reclassify as an Exceptional DC (see "10. Exceptional DC Routing"). Do not exclude or truncate it — generate a route using the BO Rule (strict tier-priority sequencing: BO1 first, then BO2, etc.) instead of the standard Score-per-km efficiency ranking, so highest-value BOs are always reached even at higher travel cost.</t>
   </si>
   <si>
+    <t xml:space="preserve">Same route/cluster set repeated across consecutive cycles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Efficiency-ranked selection alone can keep picking the same high-scoring clusters day after day if their score does not drop fast enough, leaving other assigned BOs permanently unvisited.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No explicit rule currently prevents this — recency decay only provides a soft, indirect nudge. Apply the Route Distinction Rule (sheet "11. Route Distinction Rule"): either a Repeat-Avoidance cool-down window, a Fixed Rotation beat calendar, or both layered together.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exceptional DC Routing — Conditional Ceiling &amp; the BO Rule</t>
   </si>
   <si>
@@ -985,6 +998,231 @@
   </si>
   <si>
     <t xml:space="preserve">This is the core justification for the BO Rule: Score/km and Distance-ascending orderings can both, by coincidence of the data, end up capturing similar total score within 80km — but neither one guarantees WHICH BOs are protected. In this example, Distance-Ascending actually leaves out BO102, a top-tier (BO1) outlet, if the day is cut short — precisely the failure mode the BO Rule is designed to prevent. Only tier-first sequencing guarantees no higher-tier BO is ever left behind a lower-tier one, independent of how the day actually plays out.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route Distinction / Beat Cycle Rule</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today, the only mechanism causing route-to-route variation is recency decay in the BO Scoring stage (Section 2) — a visited cluster's score drops for the next cycle, which indirectly makes it less likely to be picked again immediately. This is a soft, incidental effect, not an explicit rule: nothing currently guarantees that consecutive routes are distinct, and nothing guarantees every cluster gets visited on a predictable cadence. This sheet adds that as an explicit rule, with two alternative models.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model A — Repeat-Avoidance (Cool-down Rule)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A hard constraint: once a cluster is selected into a route, it is excluded from selection for the next N planning cycles (the "cool-down window"), even if it would otherwise rank highly. This converts the existing soft recency-decay effect into an explicit, guaranteed rule rather than a scoring nudge.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A cluster was selected (Selected? = Y) in any of the last N cycles.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effect</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That cluster is hard-excluded from the ranking pool for the current cycle, regardless of its Score-per-km.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Override</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If excluding it would leave the day's route empty or below a minimum coverage threshold, the cool-down is waived for the single highest-scoring blocked cluster (an escape hatch, not a silent failure).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cool-down window N is configurable — e.g., N=1 (can't repeat tomorrow) up to N=6 (roughly a weekly rotation).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked example — cool-down window N = 1 day, applied to the 6 standard clusters (A-F):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eligible Clusters (not in cool-down)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blocked (cooling down)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route Selected (Efficiency-ranked, budget-capped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A, B, C, D, E, F (no history yet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D, A, B, F, E (63km) — same as the standard Route 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C only (D, A, B, F, E all cooling down from Day 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D, A, B, F, E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C alone (25km) — forced, since it's the only eligible cluster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A, B, D, E, F (C now cooling down from Day 2; Day-1 clusters' cool-down has expired)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D, A, B, F, E again (63km) — cool-down has fully reset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note the trade-off visible on Day 2: forcing distinction produces a very thin route (just cluster C, 25km) because every other cluster is still cooling down. A 1-day cool-down is too aggressive for only 6 clusters — this is why the window (N) needs to be sized against the number of clusters in the territory, not set arbitrarily.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model B — Fixed Rotation (Beat Calendar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Instead of reacting after the fact (Model A), pre-assign clusters to specific days of a repeating cycle (e.g., a weekly beat calendar). Each day only draws candidates from its assigned zone; standard efficiency-ranked selection and the budget cap still apply within that zone. This guarantees a predictable visit cadence for every cluster and produces distinct routes by construction, without needing a cool-down override.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None needed — distinction is structural, not reactive. Each day's candidate pool is fixed in advance.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every cluster is guaranteed a visit at least once per cycle length (e.g., every 3 days), regardless of its score that day.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zones are drawn up front from geography/density (Stage 1 clustering output), not from daily scores — e.g., group adjacent clusters so each day's zone is still travel-efficient on its own.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within-zone selection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Route Selection Criteria (Section 3, Steps 2-4) still apply inside the day's assigned zone.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Worked example — a 3-day rotation cycle across the same 6 clusters:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle Day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assigned Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clusters in Zone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route (efficiency-ranked within zone, budget-capped)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D, A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D, A (15km) — both fit easily, budget underused</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B, F</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B, F (21km) — both fit easily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C, E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C, E (52km) — both fit, uses more of the budget due to spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zone 1 (repeats)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cycle restarts — guaranteed re-visit, 3 days since last</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note the trade-off here in the opposite direction from Model A: Zones 1 and 2 leave most of the 80km budget unused (15km and 21km respectively) because zone membership was fixed by geography, not by how much value is available that day — the guarantee of distinction/coverage comes at the cost of budget efficiency on lighter zones.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Which Rule to Use</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dimension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model A: Repeat-Avoidance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model B: Fixed Rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How distinction is achieved</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reactive — blocks recently-visited clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structural — pre-assigns clusters to fixed days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coverage guarantee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Indirect (depends on cool-down window sizing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct — every cluster visited once per cycle length, by design</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budget efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High — always picks the best-available eligible clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lower on light zones — some days under-use the travel budget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsiveness to real-time BO score changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High — still ranks by current score among eligible clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low — zone membership doesn't react to score changes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Best suited for</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dense territories with many interchangeable clusters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sparse or Exceptional DC territories needing predictable cadence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recommended default: run Model B (Fixed Rotation) as the backbone for territory-wide coverage cadence, with Model A (Repeat-Avoidance, short cool-down of 1-2 days) layered on top as a safeguard within each day's zone — this prevents the same cluster being picked two days running even within a single rotation slot, without sacrificing the predictability of the rotation.</t>
   </si>
 </sst>
 </file>
@@ -1780,7 +2018,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
@@ -1790,7 +2028,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1800,145 +2038,156 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="8" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>241</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -1981,7 +2230,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1993,7 +2242,7 @@
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2005,7 +2254,7 @@
     </row>
     <row r="4" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
@@ -2017,7 +2266,7 @@
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2029,7 +2278,7 @@
     </row>
     <row r="6" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -2049,39 +2298,39 @@
     </row>
     <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -2093,7 +2342,7 @@
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -2105,72 +2354,72 @@
     </row>
     <row r="16" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J16" s="6" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="N16" s="6" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="R16" s="39" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="S16" s="6" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B17" s="16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C17" s="16" t="n">
         <v>12</v>
@@ -2188,7 +2437,7 @@
         <v>No</v>
       </c>
       <c r="G17" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">VALUE(MID(B17,3,1))</f>
@@ -2231,7 +2480,7 @@
         <v>Y</v>
       </c>
       <c r="S17" s="24" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="T17" s="24" t="n">
         <v>100</v>
@@ -2239,10 +2488,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="B18" s="16" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C18" s="16" t="n">
         <v>25</v>
@@ -2260,7 +2509,7 @@
         <v>No</v>
       </c>
       <c r="G18" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H18" s="15" t="n">
         <f aca="false">VALUE(MID(B18,3,1))</f>
@@ -2303,7 +2552,7 @@
         <v>N</v>
       </c>
       <c r="S18" s="24" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="T18" s="24" t="n">
         <v>80</v>
@@ -2311,10 +2560,10 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B19" s="16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C19" s="16" t="n">
         <v>18</v>
@@ -2332,7 +2581,7 @@
         <v>No</v>
       </c>
       <c r="G19" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H19" s="15" t="n">
         <f aca="false">VALUE(MID(B19,3,1))</f>
@@ -2375,7 +2624,7 @@
         <v>Y</v>
       </c>
       <c r="S19" s="24" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="T19" s="24" t="n">
         <v>60</v>
@@ -2383,10 +2632,10 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="C20" s="16" t="n">
         <v>22</v>
@@ -2404,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="G20" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H20" s="15" t="n">
         <f aca="false">VALUE(MID(B20,3,1))</f>
@@ -2447,7 +2696,7 @@
         <v>Y</v>
       </c>
       <c r="S20" s="24" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="T20" s="24" t="n">
         <v>40</v>
@@ -2455,10 +2704,10 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C21" s="16" t="n">
         <v>10</v>
@@ -2476,7 +2725,7 @@
         <v>Yes — over ceiling</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H21" s="15" t="n">
         <f aca="false">VALUE(MID(B21,3,1))</f>
@@ -2519,7 +2768,7 @@
         <v>Y</v>
       </c>
       <c r="S21" s="24" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="T21" s="24" t="n">
         <v>20</v>
@@ -2527,10 +2776,10 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="B22" s="16" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C22" s="16" t="n">
         <v>8</v>
@@ -2548,7 +2797,7 @@
         <v>Yes — over ceiling</v>
       </c>
       <c r="G22" s="21" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H22" s="15" t="n">
         <f aca="false">VALUE(MID(B22,3,1))</f>
@@ -2593,7 +2842,7 @@
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="40" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B23" s="40"/>
       <c r="C23" s="27" t="n">
@@ -2601,12 +2850,12 @@
         <v>95</v>
       </c>
       <c r="F23" s="29" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -2617,7 +2866,7 @@
     </row>
     <row r="27" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
@@ -2628,7 +2877,7 @@
     </row>
     <row r="29" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2649,7 +2898,7 @@
     </row>
     <row r="30" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5"/>
@@ -2670,33 +2919,33 @@
     </row>
     <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="D32" s="18" t="str">
         <f aca="false">SUMPRODUCT(--(F17:F22="No"))&amp;" of 6"</f>
@@ -2707,18 +2956,18 @@
         <v>360</v>
       </c>
       <c r="F32" s="13" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="D33" s="20" t="str">
         <f aca="false">SUMPRODUCT(--(N17:N22="Y"))&amp;" of 6"</f>
@@ -2729,18 +2978,18 @@
         <v>380</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="23" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B34" s="37" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D34" s="22" t="str">
         <f aca="false">SUMPRODUCT(--(Q17:Q22="Y"))&amp;" of 6"</f>
@@ -2751,12 +3000,12 @@
         <v>360</v>
       </c>
       <c r="F34" s="37" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5"/>
@@ -2790,6 +3039,460 @@
     <mergeCell ref="A29:Q29"/>
     <mergeCell ref="A30:Q30"/>
     <mergeCell ref="A36:Q36"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="35"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="5" t="s">
+        <v>315</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="14" t="s">
+        <v>318</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="14" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="14" t="s">
+        <v>324</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="5" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+    </row>
+    <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="14" t="s">
+        <v>331</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" s="14" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="14" t="s">
+        <v>335</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>336</v>
+      </c>
+      <c r="C15" s="14" t="s">
+        <v>337</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5"/>
+      <c r="D18" s="5"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>344</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5"/>
+      <c r="D20" s="5"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="37" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="37" t="s">
+        <v>320</v>
+      </c>
+      <c r="B23" s="37" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="37" t="s">
+        <v>349</v>
+      </c>
+      <c r="B25" s="37" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="6" t="s">
+        <v>352</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="37" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="37" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="D29" s="37" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>359</v>
+      </c>
+      <c r="C30" s="37" t="s">
+        <v>360</v>
+      </c>
+      <c r="D30" s="37" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="37" t="s">
+        <v>339</v>
+      </c>
+      <c r="B31" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" s="37" t="s">
+        <v>363</v>
+      </c>
+      <c r="D31" s="37" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="37" t="s">
+        <v>365</v>
+      </c>
+      <c r="B32" s="37" t="s">
+        <v>366</v>
+      </c>
+      <c r="C32" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="D32" s="37" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="5" t="s">
+        <v>368</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>376</v>
+      </c>
+      <c r="B38" s="8" t="s">
+        <v>377</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>382</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="49.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A35:H35"/>
+    <mergeCell ref="A43:H43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3092,7 +3795,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="26"/>
@@ -3249,8 +3952,18 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
     </row>
+    <row r="23" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A9:F9"/>
@@ -3258,6 +3971,7 @@
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3283,7 +3997,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3293,7 +4007,7 @@
     </row>
     <row r="3" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -3311,23 +4025,23 @@
     </row>
     <row r="5" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
@@ -3337,7 +4051,7 @@
     </row>
     <row r="9" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
@@ -3347,7 +4061,7 @@
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10" s="11"/>
       <c r="C10" s="11"/>
@@ -3357,7 +4071,7 @@
     </row>
     <row r="12" customFormat="false" ht="69.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5"/>
@@ -3398,7 +4112,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3408,7 +4122,7 @@
     </row>
     <row r="3" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -3418,7 +4132,7 @@
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -3428,73 +4142,73 @@
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -3510,62 +4224,62 @@
         <v>71</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="14" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B17" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -3599,7 +4313,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3609,7 +4323,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>26</v>
@@ -3617,42 +4331,42 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>
@@ -3691,7 +4405,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3703,7 +4417,7 @@
     </row>
     <row r="3" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="5"/>
@@ -3715,60 +4429,60 @@
     </row>
     <row r="5" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P5" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>8</v>
@@ -3791,7 +4505,7 @@
         <v>9.2</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I6" s="18" t="n">
         <f aca="false">RANK(G6,$G$6:$G$11,0)+COUNTIF($G$6:G6,G6)-1</f>
@@ -3832,7 +4546,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B7" s="16" t="n">
         <v>5</v>
@@ -3855,7 +4569,7 @@
         <v>4.69230769230769</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I7" s="18" t="n">
         <f aca="false">RANK(G7,$G$6:$G$11,0)+COUNTIF($G$6:G7,G7)-1</f>
@@ -3896,7 +4610,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B8" s="16" t="n">
         <v>12</v>
@@ -3919,7 +4633,7 @@
         <v>3.12</v>
       </c>
       <c r="H8" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="I8" s="18" t="n">
         <f aca="false">RANK(G8,$G$6:$G$11,0)+COUNTIF($G$6:G8,G8)-1</f>
@@ -3960,7 +4674,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B9" s="16" t="n">
         <v>4</v>
@@ -3983,7 +4697,7 @@
         <v>11</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I9" s="18" t="n">
         <f aca="false">RANK(G9,$G$6:$G$11,0)+COUNTIF($G$6:G9,G9)-1</f>
@@ -4024,7 +4738,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B10" s="16" t="n">
         <v>7</v>
@@ -4047,7 +4761,7 @@
         <v>3.25925925925926</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I10" s="18" t="n">
         <f aca="false">RANK(G10,$G$6:$G$11,0)+COUNTIF($G$6:G10,G10)-1</f>
@@ -4088,7 +4802,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="24" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B11" s="16" t="n">
         <v>3</v>
@@ -4111,7 +4825,7 @@
         <v>3.75</v>
       </c>
       <c r="H11" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="I11" s="18" t="n">
         <f aca="false">RANK(G11,$G$6:$G$11,0)+COUNTIF($G$6:G11,G11)-1</f>
@@ -4152,7 +4866,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="26"/>
       <c r="C12" s="26"/>
@@ -4167,12 +4881,12 @@
         <v>326</v>
       </c>
       <c r="H12" s="29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="26"/>
       <c r="C13" s="26"/>
@@ -4187,7 +4901,7 @@
         <v>326</v>
       </c>
       <c r="H13" s="29" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M13" s="21" t="n">
         <f aca="false">SUMIF(N6:N11,"Y",F6:F11)</f>
@@ -4208,7 +4922,7 @@
     </row>
     <row r="14" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5"/>
@@ -4220,7 +4934,7 @@
     </row>
     <row r="15" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5"/>
@@ -4232,7 +4946,7 @@
     </row>
     <row r="16" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5"/>
@@ -4244,7 +4958,7 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -4265,7 +4979,7 @@
     </row>
     <row r="19" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5"/>
@@ -4286,33 +5000,33 @@
     </row>
     <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D21" s="18" t="n">
         <f aca="false">F13</f>
@@ -4329,13 +5043,13 @@
     </row>
     <row r="22" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="34" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B22" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D22" s="20" t="n">
         <f aca="false">M13</f>
@@ -4352,13 +5066,13 @@
     </row>
     <row r="23" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="36" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B23" s="37" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D23" s="22" t="n">
         <f aca="false">P13</f>
@@ -4375,7 +5089,7 @@
     </row>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
@@ -4431,7 +5145,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -4441,7 +5155,7 @@
     </row>
     <row r="3" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>50</v>
@@ -4449,34 +5163,34 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
